--- a/tests/agent_contract/data/06_hard_existing_target_sheet.xlsx
+++ b/tests/agent_contract/data/06_hard_existing_target_sheet.xlsx
@@ -1,93 +1,159 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单明细" sheetId="1" r:id="Rc5bef782802b49c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" r:id="R7762141c23314c03"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市汇总" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="#,##0.00"/>
-  </x:numFmts>
-  <x:fonts count="2">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1F4E78"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="4">
-    <x:border/>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9EADBA"/>
-      </x:bottom>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="9">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="4">
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EADBA"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -282,88 +348,124 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.25" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>城市</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>销售额</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="5" t="str">
-        <x:v>杭州</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C2" s="5" t="str">
-        <x:v>有效</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="5" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="str">
-        <x:v>有效</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="6" t="str">
-        <x:v>杭州</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="str">
-        <x:v>无效</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4.25" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="4.25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>无效</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="7.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.880000114440918" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>说明</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>值</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="6" t="str">
-        <x:v>现有内容</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>不可覆盖</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7.880000114440918" customWidth="1" min="1" max="1"/>
+    <col width="7.880000114440918" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>现有内容</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>不可覆盖</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>